--- a/AAII_Financials/Yearly/WHWK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WHWK_YR_FIN.xlsx
@@ -742,10 +742,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>91700</v>
+        <v>800</v>
       </c>
       <c r="E9" s="3">
-        <v>54100</v>
+        <v>3000</v>
       </c>
       <c r="F9" s="3">
         <v>51700</v>
@@ -772,10 +772,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-84600</v>
+        <v>6400</v>
       </c>
       <c r="E10" s="3">
-        <v>-28100</v>
+        <v>23000</v>
       </c>
       <c r="F10" s="3">
         <v>-27400</v>
@@ -816,10 +816,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>136700</v>
+        <v>91000</v>
       </c>
       <c r="E12" s="3">
-        <v>57000</v>
+        <v>51000</v>
       </c>
       <c r="F12" s="3">
         <v>48900</v>
